--- a/artfynd/A 2493-2026 artfynd.xlsx
+++ b/artfynd/A 2493-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130106340</v>
+        <v>130108608</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mosselbodarna, Dlr</t>
+          <t>Mosselbodarna, Dala-Floda, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485050</v>
+        <v>485120</v>
       </c>
       <c r="R2" t="n">
-        <v>6711120</v>
+        <v>6711043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Granlåga, längs med på fler ställen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,29 +769,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130108610</v>
+        <v>130106339</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,17 +815,28 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mosselbodarna, Dala-Floda, Dlr</t>
+          <t>mosselbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485114</v>
+        <v>485079</v>
       </c>
       <c r="R3" t="n">
-        <v>6711080</v>
+        <v>6711123</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,12 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Blöt sumpskog vid myr.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +894,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130108620</v>
+        <v>130106340</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,17 +934,28 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mosselbodarna, Dala-Floda, Dlr</t>
+          <t>mosselbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485080</v>
+        <v>485050</v>
       </c>
       <c r="R4" t="n">
-        <v>6711128</v>
+        <v>6711120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,28 +1006,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130108614</v>
+        <v>130108610</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485099</v>
+        <v>485114</v>
       </c>
       <c r="R5" t="n">
-        <v>6711104</v>
+        <v>6711080</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Blöt sumpskog vid myr.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,6 +1119,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130108621</v>
+        <v>130108612</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485083</v>
+        <v>485098</v>
       </c>
       <c r="R6" t="n">
-        <v>6711135</v>
+        <v>6711096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rörligt mark vatten mot myr.</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130108625</v>
+        <v>130108613</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,16 +1274,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mosselbodarna, Dala-Floda, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485044</v>
+        <v>485103</v>
       </c>
       <c r="R7" t="n">
-        <v>6711209</v>
+        <v>6711101</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1328,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fläckvis på över 100m2, blöt mark.Örtrikt markskikt..</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,6 +1342,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1340,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130108619</v>
+        <v>130108614</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485079</v>
+        <v>485099</v>
       </c>
       <c r="R8" t="n">
-        <v>6711118</v>
+        <v>6711104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130108623</v>
+        <v>130108615</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485072</v>
+        <v>485097</v>
       </c>
       <c r="R9" t="n">
-        <v>6711165</v>
+        <v>6711113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130108613</v>
+        <v>130108616</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,19 +1604,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mosselbodarna, Dala-Floda, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485103</v>
+        <v>485093</v>
       </c>
       <c r="R10" t="n">
-        <v>6711101</v>
+        <v>6711115</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,12 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fläckvis på över 100m2, blöt mark.Örtrikt markskikt..</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1664,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130108611</v>
+        <v>130108617</v>
       </c>
       <c r="B11" t="n">
-        <v>98840</v>
+        <v>91680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1693,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485112</v>
+        <v>485090</v>
       </c>
       <c r="R11" t="n">
-        <v>6711086</v>
+        <v>6711116</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1771,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1778,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130108616</v>
+        <v>130108618</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485093</v>
+        <v>485079</v>
       </c>
       <c r="R12" t="n">
-        <v>6711115</v>
+        <v>6711120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130108615</v>
+        <v>130108619</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485097</v>
+        <v>485079</v>
       </c>
       <c r="R13" t="n">
-        <v>6711113</v>
+        <v>6711118</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1965,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130108617</v>
+        <v>130108620</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485090</v>
+        <v>485080</v>
       </c>
       <c r="R14" t="n">
-        <v>6711116</v>
+        <v>6711128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2072,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130108626</v>
+        <v>130108621</v>
       </c>
       <c r="B15" t="n">
-        <v>97794</v>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,21 +2121,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2134,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485044</v>
+        <v>485083</v>
       </c>
       <c r="R15" t="n">
-        <v>6711264</v>
+        <v>6711135</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2179,7 +2190,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rörligt mark vatten mot myr.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130108618</v>
+        <v>130108622</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485079</v>
+        <v>485087</v>
       </c>
       <c r="R16" t="n">
-        <v>6711120</v>
+        <v>6711147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2276,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2286,7 +2302,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,6 +2311,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130106339</v>
+        <v>130108623</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,28 +2358,17 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mosselbodarna, Dlr</t>
+          <t>Mosselbodarna, Dala-Floda, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485079</v>
+        <v>485072</v>
       </c>
       <c r="R17" t="n">
-        <v>6711123</v>
+        <v>6711165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2400,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2404,7 +2410,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,29 +2419,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108622</v>
+        <v>130108625</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2467,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485087</v>
+        <v>485044</v>
       </c>
       <c r="R18" t="n">
-        <v>6711147</v>
+        <v>6711209</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,7 +2507,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2517,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,7 +2526,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2540,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108612</v>
+        <v>130126332</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,34 +2555,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mosselbodarna, Dala-Floda, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485098</v>
+        <v>485111</v>
       </c>
       <c r="R19" t="n">
-        <v>6711096</v>
+        <v>6710958</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,15 +2627,21 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Troligen fler naturvårdsarter på den gamla, grova sälgen. Naturvårdsträd!</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2647,32 +2660,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130108608</v>
+        <v>130108611</v>
       </c>
       <c r="B20" t="n">
-        <v>91757</v>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2682,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485120</v>
+        <v>485112</v>
       </c>
       <c r="R20" t="n">
-        <v>6711043</v>
+        <v>6711086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,7 +2730,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2727,12 +2740,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Granlåga, längs med på fler ställen.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,6 +2749,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2756,6 +2765,113 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130108626</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mosselbodarna, Dala-Floda, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>485044</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6711264</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2493-2026 artfynd.xlsx
+++ b/artfynd/A 2493-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108608</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106339</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106340</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108610</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108612</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108613</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108614</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108615</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108616</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1786,6 +1836,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108617</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108618</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108619</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108620</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2219,6 +2289,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108621</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108622</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,6 +2514,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108623</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2541,6 +2626,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108625</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2657,6 +2747,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130126332</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2765,6 +2860,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108611</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,8 +2972,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108626</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>